--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T09:44:41+05:30</t>
+    <t>Generated 2026-07-04T09:50:02+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:42:38+05:30 (2m3s ago)</t>
+    <t>2026-07-04T09:48:02+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -522,10 +522,16 @@
     <t>09:42:38.105</t>
   </si>
   <si>
+    <t>2026-07-04T09:47:42.3869041+05:30</t>
+  </si>
+  <si>
+    <t>09:47:42.386</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T09:44:41+05:30</t>
+    <t>2026-07-04T09:50:02+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1120,7 +1126,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 20s</t>
+          <t>0h 7m 41s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1150,7 +1156,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>09:44:41</t>
+          <t>09:50:02</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1213,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>295.0</t>
+          <t>234.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>202114.2</t>
+          <t>210203.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>463</t>
+          <t>1858</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1227,7 +1233,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>341</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1247,7 +1253,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>88h 58m 39s</t>
+          <t>88h 58m 49s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1257,7 +1263,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>09:44:41</t>
+          <t>09:50:02</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1382,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T09:42:38.1051654+05:30</t>
+          <t>2026-07-04T09:47:42.3869041+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1386,7 +1392,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:42:38.105</t>
+          <t>09:47:42.386</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -3973,18 +3979,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="s">
+    <row r="75">
+      <c r="A75" s="4">
+        <v>58</v>
+      </c>
+      <c r="B75" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C75" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="D76" t="s">
+      <c r="E75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F75" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H75" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I75" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J75" s="4">
+        <v>0</v>
+      </c>
+      <c r="K75" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L75" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="s">
         <v>170</v>
       </c>
-      <c r="E76">
-        <v>57</v>
+      <c r="B77" t="s">
+        <v>171</v>
+      </c>
+      <c r="D77" t="s">
+        <v>172</v>
+      </c>
+      <c r="E77">
+        <v>58</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="173">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T09:50:02+05:30</t>
+    <t>Generated 2026-07-04T09:54:59+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:48:02+05:30 (2m0s ago)</t>
+    <t>2026-07-04T09:53:24+05:30 (1m35s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>6</t>
   </si>
   <si>
     <t>Last error</t>
@@ -528,10 +528,16 @@
     <t>09:47:42.386</t>
   </si>
   <si>
+    <t>2026-07-04T09:52:42.5062659+05:30</t>
+  </si>
+  <si>
+    <t>09:52:42.506</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T09:50:02+05:30</t>
+    <t>2026-07-04T09:54:59+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1126,7 +1132,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 41s</t>
+          <t>0h 12m 38s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1146,7 +1152,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>88h 58m 49s</t>
+          <t>89h 1m 14s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1156,7 +1162,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>09:50:02</t>
+          <t>09:54:59</t>
         </is>
       </c>
     </row>
@@ -1213,17 +1219,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>234.0</t>
+          <t>151.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>210203.2</t>
+          <t>90758.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1858</t>
+          <t>3346</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1233,7 +1239,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t>664</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1253,7 +1259,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>88h 58m 49s</t>
+          <t>88h 59m 59s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1263,7 +1269,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>09:50:02</t>
+          <t>09:54:59</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1388,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T09:47:42.3869041+05:30</t>
+          <t>2026-07-04T09:52:42.5062659+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1392,7 +1398,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:47:42.386</t>
+          <t>09:52:42.506</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4017,18 +4023,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="s">
+    <row r="76">
+      <c r="A76" s="4">
+        <v>59</v>
+      </c>
+      <c r="B76" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C76" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="D77" t="s">
+      <c r="E76" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H76" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I76" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J76" s="4">
+        <v>0</v>
+      </c>
+      <c r="K76" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L76" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="s">
         <v>172</v>
       </c>
-      <c r="E77">
-        <v>58</v>
+      <c r="B78" t="s">
+        <v>173</v>
+      </c>
+      <c r="D78" t="s">
+        <v>174</v>
+      </c>
+      <c r="E78">
+        <v>59</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T09:54:59+05:30</t>
+    <t>Generated 2026-07-04T09:55:24+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:53:24+05:30 (1m35s ago)</t>
+    <t>2026-07-04T09:53:24+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -537,7 +537,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T09:54:59+05:30</t>
+    <t>2026-07-04T09:55:24+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1132,7 +1132,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 38s</t>
+          <t>0h 13m 3s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 1m 14s</t>
+          <t>89h 1m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>09:54:59</t>
+          <t>09:55:24</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1219,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>151.0</t>
+          <t>120.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>90758.2</t>
+          <t>163653.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3346</t>
+          <t>3494</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1269,7 +1269,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>09:54:59</t>
+          <t>09:55:24</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T09:55:24+05:30</t>
+    <t>Generated 2026-07-04T09:59:55+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:53:24+05:30 (2m0s ago)</t>
+    <t>2026-07-04T09:58:40+05:30 (1m15s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>6</t>
+    <t>10</t>
   </si>
   <si>
     <t>Last error</t>
@@ -534,10 +534,16 @@
     <t>09:52:42.506</t>
   </si>
   <si>
+    <t>2026-07-04T09:57:42.3233669+05:30</t>
+  </si>
+  <si>
+    <t>09:57:42.323</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T09:55:24+05:30</t>
+    <t>2026-07-04T09:59:55+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1132,7 +1138,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 13m 3s</t>
+          <t>0h 17m 34s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1152,7 +1158,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 1m 29s</t>
+          <t>89h 2m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1162,7 +1168,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>09:55:24</t>
+          <t>09:59:55</t>
         </is>
       </c>
     </row>
@@ -1219,17 +1225,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>120.0</t>
+          <t>187.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>163653.6</t>
+          <t>186255.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3494</t>
+          <t>4861</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1239,7 +1245,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1259,7 +1265,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>88h 59m 59s</t>
+          <t>89h 2m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1269,7 +1275,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>09:55:24</t>
+          <t>09:59:55</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1394,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T09:52:42.5062659+05:30</t>
+          <t>2026-07-04T09:57:42.3233669+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1398,7 +1404,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:52:42.506</t>
+          <t>09:57:42.323</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4061,18 +4067,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" t="s">
+    <row r="77">
+      <c r="A77" s="4">
+        <v>60</v>
+      </c>
+      <c r="B77" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C77" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="D78" t="s">
+      <c r="E77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F77" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H77" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I77" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J77" s="4">
+        <v>0</v>
+      </c>
+      <c r="K77" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L77" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="s">
         <v>174</v>
       </c>
-      <c r="E78">
-        <v>59</v>
+      <c r="B79" t="s">
+        <v>175</v>
+      </c>
+      <c r="D79" t="s">
+        <v>176</v>
+      </c>
+      <c r="E79">
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T09:59:55+05:30</t>
+    <t>Generated 2026-07-04T10:00:18+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:58:40+05:30 (1m15s ago)</t>
+    <t>2026-07-04T09:58:40+05:30 (1m38s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -543,7 +543,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T09:59:55+05:30</t>
+    <t>2026-07-04T10:00:18+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 34s</t>
+          <t>0h 17m 57s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>09:59:55</t>
+          <t>10:00:18</t>
         </is>
       </c>
     </row>
@@ -1225,17 +1225,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>187.0</t>
+          <t>192.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>186255.4</t>
+          <t>186321.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4938</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>09:59:55</t>
+          <t>10:00:18</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:00:18+05:30</t>
+    <t>Generated 2026-07-04T10:00:40+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:58:40+05:30 (1m38s ago)</t>
+    <t>2026-07-04T09:58:40+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -543,7 +543,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:00:18+05:30</t>
+    <t>2026-07-04T10:00:40+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1138,7 +1138,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 57s</t>
+          <t>0h 18m 19s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 2m 19s</t>
+          <t>89h 2m 24s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1168,7 +1168,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:00:18</t>
+          <t>10:00:40</t>
         </is>
       </c>
     </row>
@@ -1225,17 +1225,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>192.0</t>
+          <t>184.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>186321.0</t>
+          <t>186201.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>4938</t>
+          <t>5045</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:00:18</t>
+          <t>10:00:40</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:00:40+05:30</t>
+    <t>Generated 2026-07-04T10:04:55+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T09:58:40+05:30 (2m0s ago)</t>
+    <t>2026-07-04T10:03:55+05:30 (1m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>10</t>
+    <t>15</t>
   </si>
   <si>
     <t>Last error</t>
@@ -540,10 +540,22 @@
     <t>09:57:42.323</t>
   </si>
   <si>
+    <t>2026-07-04T10:02:42.3106086+05:30</t>
+  </si>
+  <si>
+    <t>10:02:42.310</t>
+  </si>
+  <si>
+    <t>2026-07-04T10:03:55.6786002+05:30</t>
+  </si>
+  <si>
+    <t>10:03:55.678</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:00:40+05:30</t>
+    <t>2026-07-04T10:04:55+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1138,7 +1150,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 18m 19s</t>
+          <t>0h 22m 34s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1158,7 +1170,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 2m 24s</t>
+          <t>89h 4m 59s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1168,7 +1180,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:00:40</t>
+          <t>10:04:55</t>
         </is>
       </c>
     </row>
@@ -1225,17 +1237,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>184.0</t>
+          <t>253.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>186201.0</t>
+          <t>268651.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5045</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1245,7 +1257,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>1295</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1265,7 +1277,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 2m 19s</t>
+          <t>89h 4m 29s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1275,7 +1287,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:00:40</t>
+          <t>10:04:55</t>
         </is>
       </c>
     </row>
@@ -1394,7 +1406,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T09:57:42.3233669+05:30</t>
+          <t>2026-07-04T10:03:55.6786002+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1404,7 +1416,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>09:57:42.323</t>
+          <t>10:03:55.678</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4105,18 +4117,94 @@
         <v>44</v>
       </c>
     </row>
+    <row r="78">
+      <c r="A78" s="4">
+        <v>61</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="E78" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H78" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I78" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J78" s="4">
+        <v>0</v>
+      </c>
+      <c r="K78" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L78" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="79">
-      <c r="A79" t="s">
-        <v>174</v>
-      </c>
-      <c r="B79" t="s">
-        <v>175</v>
-      </c>
-      <c r="D79" t="s">
+      <c r="A79" s="4">
+        <v>62</v>
+      </c>
+      <c r="B79" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="E79">
-        <v>60</v>
+      <c r="C79" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F79" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H79" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I79" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J79" s="4">
+        <v>0</v>
+      </c>
+      <c r="K79" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L79" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="s">
+        <v>178</v>
+      </c>
+      <c r="B81" t="s">
+        <v>179</v>
+      </c>
+      <c r="D81" t="s">
+        <v>180</v>
+      </c>
+      <c r="E81">
+        <v>62</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:04:55+05:30</t>
+    <t>Generated 2026-07-04T10:05:14+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:03:55+05:30 (1m0s ago)</t>
+    <t>2026-07-04T10:03:55+05:30 (1m18s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -555,7 +555,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:04:55+05:30</t>
+    <t>2026-07-04T10:05:14+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 34s</t>
+          <t>0h 22m 53s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 4m 59s</t>
+          <t>89h 5m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:04:55</t>
+          <t>10:05:14</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1237,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>253.0</t>
+          <t>302.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>268651.0</t>
+          <t>268657.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>6244</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:04:55</t>
+          <t>10:05:14</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:05:14+05:30</t>
+    <t>Generated 2026-07-04T10:05:36+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:03:55+05:30 (1m18s ago)</t>
+    <t>2026-07-04T10:03:55+05:30 (1m40s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -555,7 +555,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:05:14+05:30</t>
+    <t>2026-07-04T10:05:36+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 22m 53s</t>
+          <t>0h 23m 15s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 5m 19s</t>
+          <t>89h 5m 39s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:05:14</t>
+          <t>10:05:36</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>302.0</t>
+          <t>182.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6244</t>
+          <t>6341</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:05:14</t>
+          <t>10:05:36</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:05:36+05:30</t>
+    <t>Generated 2026-07-04T10:05:55+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:03:55+05:30 (1m40s ago)</t>
+    <t>2026-07-04T10:03:55+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -555,7 +555,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:05:36+05:30</t>
+    <t>2026-07-04T10:05:55+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 15s</t>
+          <t>0h 23m 34s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 5m 39s</t>
+          <t>89h 5m 59s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1180,7 +1180,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:05:36</t>
+          <t>10:05:55</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1237,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>182.0</t>
+          <t>156.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>268657.0</t>
+          <t>268627.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6341</t>
+          <t>6415</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1287,7 +1287,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:05:36</t>
+          <t>10:05:55</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="181" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:05:55+05:30</t>
+    <t>Generated 2026-07-04T10:10:02+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:03:55+05:30 (2m0s ago)</t>
+    <t>2026-07-04T10:09:08+05:30 (54s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>15</t>
+    <t>19</t>
   </si>
   <si>
     <t>Last error</t>
@@ -552,10 +552,22 @@
     <t>10:03:55.678</t>
   </si>
   <si>
+    <t>2026-07-04T10:08:02.5453131+05:30</t>
+  </si>
+  <si>
+    <t>10:08:02.545</t>
+  </si>
+  <si>
+    <t>2026-07-04T10:09:08.52269+05:30</t>
+  </si>
+  <si>
+    <t>10:09:08.522</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:05:55+05:30</t>
+    <t>2026-07-04T10:10:02+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1150,7 +1162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 23m 34s</t>
+          <t>0h 27m 41s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1170,7 +1182,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 5m 59s</t>
+          <t>89h 10m 4s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1180,7 +1192,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:05:55</t>
+          <t>10:10:02</t>
         </is>
       </c>
     </row>
@@ -1237,17 +1249,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>156.0</t>
+          <t>466.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>268627.0</t>
+          <t>268660.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>6415</t>
+          <t>7081</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1257,7 +1269,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1295</t>
+          <t>1608</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1277,7 +1289,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 4m 29s</t>
+          <t>89h 9m 14s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1287,7 +1299,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:05:55</t>
+          <t>10:10:02</t>
         </is>
       </c>
     </row>
@@ -1406,7 +1418,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T10:03:55.6786002+05:30</t>
+          <t>2026-07-04T10:09:08.52269+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1416,7 +1428,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:03:55.678</t>
+          <t>10:09:08.522</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4193,18 +4205,94 @@
         <v>44</v>
       </c>
     </row>
+    <row r="80">
+      <c r="A80" s="4">
+        <v>63</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="E80" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G80" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H80" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I80" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J80" s="4">
+        <v>0</v>
+      </c>
+      <c r="K80" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L80" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="81">
-      <c r="A81" t="s">
-        <v>178</v>
-      </c>
-      <c r="B81" t="s">
-        <v>179</v>
-      </c>
-      <c r="D81" t="s">
+      <c r="A81" s="4">
+        <v>64</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="E81">
-        <v>62</v>
+      <c r="C81" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="E81" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F81" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H81" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I81" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J81" s="4">
+        <v>0</v>
+      </c>
+      <c r="K81" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L81" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="s">
+        <v>182</v>
+      </c>
+      <c r="B83" t="s">
+        <v>183</v>
+      </c>
+      <c r="D83" t="s">
+        <v>184</v>
+      </c>
+      <c r="E83">
+        <v>64</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:10:02+05:30</t>
+    <t>Generated 2026-07-04T10:10:30+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:09:08+05:30 (54s ago)</t>
+    <t>2026-07-04T10:09:08+05:30 (1m21s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -567,7 +567,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:10:02+05:30</t>
+    <t>2026-07-04T10:10:30+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 27m 41s</t>
+          <t>0h 28m 9s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1182,7 +1182,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 10m 4s</t>
+          <t>89h 10m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:10:02</t>
+          <t>10:10:30</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>466.0</t>
+          <t>674.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>268660.4</t>
+          <t>268491.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7081</t>
+          <t>7134</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:10:02</t>
+          <t>10:10:30</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:10:30+05:30</t>
+    <t>Generated 2026-07-04T10:10:48+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:09:08+05:30 (1m21s ago)</t>
+    <t>2026-07-04T10:09:08+05:30 (1m40s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -567,7 +567,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:10:30+05:30</t>
+    <t>2026-07-04T10:10:48+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 9s</t>
+          <t>0h 28m 27s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:10:30</t>
+          <t>10:10:48</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>674.0</t>
+          <t>520.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>268491.4</t>
+          <t>190249.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7134</t>
+          <t>7161</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:10:30</t>
+          <t>10:10:48</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:10:48+05:30</t>
+    <t>Generated 2026-07-04T10:11:08+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:09:08+05:30 (1m40s ago)</t>
+    <t>2026-07-04T10:09:08+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -567,7 +567,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:10:48+05:30</t>
+    <t>2026-07-04T10:11:08+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 27s</t>
+          <t>0h 28m 47s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:10:48</t>
+          <t>10:11:08</t>
         </is>
       </c>
     </row>
@@ -1249,17 +1249,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>520.0</t>
+          <t>515.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>190249.0</t>
+          <t>178730.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7161</t>
+          <t>7200</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1299,7 +1299,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:10:48</t>
+          <t>10:11:08</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="185" uniqueCount="185">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:11:08+05:30</t>
+    <t>Generated 2026-07-04T10:15:01+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:09:08+05:30 (2m0s ago)</t>
+    <t>2026-07-04T10:13:31+05:30 (1m30s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>19</t>
+    <t>22</t>
   </si>
   <si>
     <t>Last error</t>
@@ -564,10 +564,16 @@
     <t>10:09:08.522</t>
   </si>
   <si>
+    <t>2026-07-04T10:13:01.4343984+05:30</t>
+  </si>
+  <si>
+    <t>10:13:01.434</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:11:08+05:30</t>
+    <t>2026-07-04T10:15:01+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1127,7 +1133,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>server+agent</t>
+          <t>agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1162,7 +1168,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 28m 47s</t>
+          <t>0h 32m 40s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1182,7 +1188,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 10m 29s</t>
+          <t>89h 12m 49s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1192,7 +1198,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:11:08</t>
+          <t>10:15:01</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1230,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>amd64</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1234,42 +1240,42 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>disconnected</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>self</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>good</t>
+          <t>offline</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>515.0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>178730.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>7200</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>1608</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1279,17 +1285,17 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>Jul 1 07:09 PM</t>
+          <t>—</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:21</t>
+          <t>—</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 9m 14s</t>
+          <t>—</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1299,7 +1305,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:11:08</t>
+          <t>10:15:01</t>
         </is>
       </c>
     </row>
@@ -1418,7 +1424,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T10:09:08.52269+05:30</t>
+          <t>2026-07-04T10:13:01.4343984+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1428,7 +1434,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:09:08.522</t>
+          <t>10:13:01.434</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4281,18 +4287,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="s">
+    <row r="82">
+      <c r="A82" s="4">
+        <v>65</v>
+      </c>
+      <c r="B82" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C82" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="D83" t="s">
+      <c r="E82" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" s="4">
+        <v>0</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="s">
         <v>184</v>
       </c>
-      <c r="E83">
-        <v>64</v>
+      <c r="B84" t="s">
+        <v>185</v>
+      </c>
+      <c r="D84" t="s">
+        <v>186</v>
+      </c>
+      <c r="E84">
+        <v>65</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:15:01+05:30</t>
+    <t>Generated 2026-07-04T10:15:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:13:31+05:30 (1m30s ago)</t>
+    <t>2026-07-04T10:13:31+05:30 (1m46s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -573,7 +573,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:15:01+05:30</t>
+    <t>2026-07-04T10:15:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 32m 40s</t>
+          <t>0h 32m 56s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:15:01</t>
+          <t>10:15:17</t>
         </is>
       </c>
     </row>
@@ -1305,7 +1305,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:15:01</t>
+          <t>10:15:17</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,230 +16,233 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="187">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:15:17+05:30</t>
+    <t>Generated 2026-07-04T10:45:11+05:30</t>
   </si>
   <si>
     <t>Election method</t>
   </si>
   <si>
+    <t>none</t>
+  </si>
+  <si>
+    <t>GitHub configured</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>GitHub repo</t>
+  </si>
+  <si>
+    <t>puniteswra-spec/PU</t>
+  </si>
+  <si>
+    <t>Self AgentID</t>
+  </si>
+  <si>
+    <t>SAATHII-TB-b19900d6</t>
+  </si>
+  <si>
+    <t>Self hostname</t>
+  </si>
+  <si>
+    <t>SAATHII-TB</t>
+  </si>
+  <si>
+    <t>Mode / Role</t>
+  </si>
+  <si>
+    <t>SERVER (primary)</t>
+  </si>
+  <si>
+    <t>Self is leader</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Current leader</t>
+  </si>
+  <si>
+    <t>(no leader recorded)</t>
+  </si>
+  <si>
+    <t>Leader last update</t>
+  </si>
+  <si>
+    <t>(never)</t>
+  </si>
+  <si>
+    <t>Leader stale?</t>
+  </si>
+  <si>
+    <t>Last check</t>
+  </si>
+  <si>
+    <t>Check count</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>Last error</t>
+  </si>
+  <si>
+    <t>(none)</t>
+  </si>
+  <si>
+    <t>Election History (row-wise — latest first)</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>Timestamp</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Time</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Agent ID (self)</t>
+  </si>
+  <si>
+    <t>Hostname</t>
+  </si>
+  <si>
+    <t>Leader ID</t>
+  </si>
+  <si>
+    <t>Leader Age (sec)</t>
+  </si>
+  <si>
+    <t>Result</t>
+  </si>
+  <si>
+    <t>Error</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:26:16.0400316+05:30</t>
+  </si>
+  <si>
+    <t>2026-06-21</t>
+  </si>
+  <si>
+    <t>00:26:16.040</t>
+  </si>
+  <si>
+    <t>checking</t>
+  </si>
+  <si>
+    <t>relay</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>2026-06-21T00:27:20.780257+05:30</t>
+  </si>
+  <si>
+    <t>00:27:20.780</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:28:25.0559193+05:30</t>
+  </si>
+  <si>
+    <t>00:28:25.055</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:29:29.3402495+05:30</t>
+  </si>
+  <si>
+    <t>00:29:29.340</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:31:06.3026253+05:30</t>
+  </si>
+  <si>
+    <t>00:31:06.302</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:32:10.1868512+05:30</t>
+  </si>
+  <si>
+    <t>00:32:10.186</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:33:15.1968051+05:30</t>
+  </si>
+  <si>
+    <t>00:33:15.196</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:34:20.5951696+05:30</t>
+  </si>
+  <si>
+    <t>00:34:20.595</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:35:25.0863472+05:30</t>
+  </si>
+  <si>
+    <t>00:35:25.086</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:36:29.7546966+05:30</t>
+  </si>
+  <si>
+    <t>00:36:29.754</t>
+  </si>
+  <si>
+    <t>2026-06-21T00:38:06.3055641+05:30</t>
+  </si>
+  <si>
+    <t>00:38:06.305</t>
+  </si>
+  <si>
+    <t>2026-06-21T08:18:46.5657032+05:30</t>
+  </si>
+  <si>
+    <t>08:18:46.565</t>
+  </si>
+  <si>
+    <t>2026-06-21T11:18:23.0368316+05:30</t>
+  </si>
+  <si>
+    <t>11:18:23.036</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:12:45.7658982+05:30</t>
+  </si>
+  <si>
+    <t>12:12:45.765</t>
+  </si>
+  <si>
+    <t>2026-06-21T12:16:02.344454+05:30</t>
+  </si>
+  <si>
+    <t>12:16:02.344</t>
+  </si>
+  <si>
+    <t>renewed</t>
+  </si>
+  <si>
     <t>github</t>
   </si>
   <si>
-    <t>GitHub configured</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>GitHub repo</t>
-  </si>
-  <si>
-    <t>puniteswra-spec/PU</t>
-  </si>
-  <si>
-    <t>Self AgentID</t>
-  </si>
-  <si>
-    <t>SAATHII-TB-b19900d6</t>
-  </si>
-  <si>
-    <t>Self hostname</t>
-  </si>
-  <si>
-    <t>SAATHII-TB</t>
-  </si>
-  <si>
-    <t>Mode / Role</t>
-  </si>
-  <si>
-    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
-  </si>
-  <si>
-    <t>Self is leader</t>
-  </si>
-  <si>
-    <t>YES — this instance is the primary server</t>
-  </si>
-  <si>
-    <t>Current leader</t>
-  </si>
-  <si>
-    <t>Leader last update</t>
-  </si>
-  <si>
-    <t>2026-07-04T10:13:31+05:30 (1m46s ago)</t>
-  </si>
-  <si>
-    <t>Leader stale?</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Last check</t>
-  </si>
-  <si>
-    <t>Check count</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>Last error</t>
-  </si>
-  <si>
-    <t>(none)</t>
-  </si>
-  <si>
-    <t>Election History (row-wise — latest first)</t>
-  </si>
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>Timestamp</t>
-  </si>
-  <si>
-    <t>Date</t>
-  </si>
-  <si>
-    <t>Time</t>
-  </si>
-  <si>
-    <t>Action</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Agent ID (self)</t>
-  </si>
-  <si>
-    <t>Hostname</t>
-  </si>
-  <si>
-    <t>Leader ID</t>
-  </si>
-  <si>
-    <t>Leader Age (sec)</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Error</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:26:16.0400316+05:30</t>
-  </si>
-  <si>
-    <t>2026-06-21</t>
-  </si>
-  <si>
-    <t>00:26:16.040</t>
-  </si>
-  <si>
-    <t>checking</t>
-  </si>
-  <si>
-    <t>relay</t>
-  </si>
-  <si>
-    <t/>
-  </si>
-  <si>
-    <t>2026-06-21T00:27:20.780257+05:30</t>
-  </si>
-  <si>
-    <t>00:27:20.780</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:28:25.0559193+05:30</t>
-  </si>
-  <si>
-    <t>00:28:25.055</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:29:29.3402495+05:30</t>
-  </si>
-  <si>
-    <t>00:29:29.340</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:31:06.3026253+05:30</t>
-  </si>
-  <si>
-    <t>00:31:06.302</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:32:10.1868512+05:30</t>
-  </si>
-  <si>
-    <t>00:32:10.186</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:33:15.1968051+05:30</t>
-  </si>
-  <si>
-    <t>00:33:15.196</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:34:20.5951696+05:30</t>
-  </si>
-  <si>
-    <t>00:34:20.595</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:35:25.0863472+05:30</t>
-  </si>
-  <si>
-    <t>00:35:25.086</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:36:29.7546966+05:30</t>
-  </si>
-  <si>
-    <t>00:36:29.754</t>
-  </si>
-  <si>
-    <t>2026-06-21T00:38:06.3055641+05:30</t>
-  </si>
-  <si>
-    <t>00:38:06.305</t>
-  </si>
-  <si>
-    <t>2026-06-21T08:18:46.5657032+05:30</t>
-  </si>
-  <si>
-    <t>08:18:46.565</t>
-  </si>
-  <si>
-    <t>2026-06-21T11:18:23.0368316+05:30</t>
-  </si>
-  <si>
-    <t>11:18:23.036</t>
-  </si>
-  <si>
-    <t>2026-06-21T12:12:45.7658982+05:30</t>
-  </si>
-  <si>
-    <t>12:12:45.765</t>
-  </si>
-  <si>
-    <t>2026-06-21T12:16:02.344454+05:30</t>
-  </si>
-  <si>
-    <t>12:16:02.344</t>
-  </si>
-  <si>
-    <t>renewed</t>
-  </si>
-  <si>
     <t>2026-06-22T07:56:01.8822385+05:30</t>
   </si>
   <si>
@@ -573,7 +576,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:15:17+05:30</t>
+    <t>2026-07-04T10:45:11+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1133,7 +1136,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>agent</t>
+          <t>server+agent</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -1168,12 +1171,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 32m 56s</t>
+          <t>0h 2m 27s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:21</t>
+          <t>2026-07-04 10:42:43</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1183,12 +1186,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-07-04 09:42:21</t>
+          <t>2026-07-04 10:42:43</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 12m 49s</t>
+          <t>89h 24m 59s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1198,7 +1201,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:15:17</t>
+          <t>10:45:11</t>
         </is>
       </c>
     </row>
@@ -1230,72 +1233,72 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>amd64</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>10.0.62</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>agent</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>self</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>good</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>919.0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>178358.6</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>566</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>10.0.62</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>disconnected</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>offline</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Jul 1 07:09 PM</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-07-04 10:42:43</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>89h 24m 9s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1305,7 +1308,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:15:17</t>
+          <t>10:45:11</t>
         </is>
       </c>
     </row>
@@ -1758,23 +1761,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1782,7 +1785,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="13">
@@ -2404,7 +2407,7 @@
         <v>73</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>9</v>
@@ -2430,19 +2433,19 @@
         <v>16</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>9</v>
@@ -2457,10 +2460,10 @@
         <v>9223372036</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L33" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -2468,19 +2471,19 @@
         <v>17</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>9</v>
@@ -2495,10 +2498,10 @@
         <v>9223372036</v>
       </c>
       <c r="K34" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L34" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2506,19 +2509,19 @@
         <v>18</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>9</v>
@@ -2533,10 +2536,10 @@
         <v>9223372036</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -2544,19 +2547,19 @@
         <v>19</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>9</v>
@@ -2571,10 +2574,10 @@
         <v>9223372036</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L36" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="37">
@@ -2582,19 +2585,19 @@
         <v>20</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>9</v>
@@ -2609,10 +2612,10 @@
         <v>9223372036</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="L37" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -2620,19 +2623,19 @@
         <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C38" s="4" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E38" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>9</v>
@@ -2658,19 +2661,19 @@
         <v>22</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>9</v>
@@ -2685,7 +2688,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>44</v>
@@ -2696,19 +2699,19 @@
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C40" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E40" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>9</v>
@@ -2734,19 +2737,19 @@
         <v>24</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E41" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>9</v>
@@ -2772,19 +2775,19 @@
         <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C42" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E42" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>9</v>
@@ -2810,19 +2813,19 @@
         <v>26</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C43" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E43" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>9</v>
@@ -2848,19 +2851,19 @@
         <v>27</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C44" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E44" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>9</v>
@@ -2886,19 +2889,19 @@
         <v>28</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E45" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>9</v>
@@ -2924,19 +2927,19 @@
         <v>29</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>9</v>
@@ -2962,19 +2965,19 @@
         <v>30</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="E47" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>9</v>
@@ -3000,19 +3003,19 @@
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C48" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E48" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>9</v>
@@ -3038,19 +3041,19 @@
         <v>32</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C49" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E49" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>9</v>
@@ -3076,19 +3079,19 @@
         <v>33</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C50" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E50" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>9</v>
@@ -3114,19 +3117,19 @@
         <v>34</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E51" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>9</v>
@@ -3152,19 +3155,19 @@
         <v>35</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C52" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E52" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>9</v>
@@ -3190,19 +3193,19 @@
         <v>36</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="C53" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E53" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>9</v>
@@ -3228,19 +3231,19 @@
         <v>37</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C54" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E54" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>9</v>
@@ -3266,19 +3269,19 @@
         <v>38</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C55" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E55" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>9</v>
@@ -3304,19 +3307,19 @@
         <v>39</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C56" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E56" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>9</v>
@@ -3342,19 +3345,19 @@
         <v>40</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C57" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="E57" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>9</v>
@@ -3380,19 +3383,19 @@
         <v>41</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E58" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>9</v>
@@ -3418,19 +3421,19 @@
         <v>42</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E59" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>9</v>
@@ -3456,19 +3459,19 @@
         <v>43</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="C60" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E60" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>9</v>
@@ -3494,19 +3497,19 @@
         <v>44</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C61" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E61" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>9</v>
@@ -3532,19 +3535,19 @@
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E62" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>9</v>
@@ -3570,19 +3573,19 @@
         <v>46</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C63" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E63" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>9</v>
@@ -3608,19 +3611,19 @@
         <v>47</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E64" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>9</v>
@@ -3646,19 +3649,19 @@
         <v>48</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C65" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E65" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>9</v>
@@ -3684,19 +3687,19 @@
         <v>49</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E66" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>9</v>
@@ -3722,19 +3725,19 @@
         <v>50</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C67" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E67" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>9</v>
@@ -3760,19 +3763,19 @@
         <v>51</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C68" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E68" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>9</v>
@@ -3798,19 +3801,19 @@
         <v>52</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C69" s="4" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E69" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>9</v>
@@ -3836,19 +3839,19 @@
         <v>53</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C70" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E70" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>9</v>
@@ -3874,19 +3877,19 @@
         <v>54</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C71" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E71" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>9</v>
@@ -3912,19 +3915,19 @@
         <v>55</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E72" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>9</v>
@@ -3950,19 +3953,19 @@
         <v>56</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C73" s="4" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E73" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>9</v>
@@ -3988,19 +3991,19 @@
         <v>57</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E74" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>9</v>
@@ -4026,19 +4029,19 @@
         <v>58</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C75" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E75" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>9</v>
@@ -4064,19 +4067,19 @@
         <v>59</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C76" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E76" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>9</v>
@@ -4102,19 +4105,19 @@
         <v>60</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C77" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="E77" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>9</v>
@@ -4140,19 +4143,19 @@
         <v>61</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C78" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E78" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>9</v>
@@ -4178,19 +4181,19 @@
         <v>62</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C79" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="E79" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>9</v>
@@ -4216,19 +4219,19 @@
         <v>63</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C80" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E80" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>9</v>
@@ -4254,19 +4257,19 @@
         <v>64</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C81" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="E81" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>9</v>
@@ -4292,19 +4295,19 @@
         <v>65</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E82" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>3</v>
+        <v>74</v>
       </c>
       <c r="G82" s="4" t="s">
         <v>9</v>
@@ -4327,13 +4330,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B84" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="D84" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="E84">
         <v>65</v>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,18 +16,18 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:45:11+05:30</t>
+    <t>Generated 2026-07-04T10:50:22+05:30</t>
   </si>
   <si>
     <t>Election method</t>
   </si>
   <si>
-    <t>none</t>
+    <t>github</t>
   </si>
   <si>
     <t>GitHub configured</t>
@@ -57,37 +57,37 @@
     <t>Mode / Role</t>
   </si>
   <si>
-    <t>SERVER (primary)</t>
+    <t>SERVER+LEADER (this instance is the GitHub primary)</t>
   </si>
   <si>
     <t>Self is leader</t>
   </si>
   <si>
+    <t>YES — this instance is the primary server</t>
+  </si>
+  <si>
+    <t>Current leader</t>
+  </si>
+  <si>
+    <t>Leader last update</t>
+  </si>
+  <si>
+    <t>2026-07-04T10:48:22+05:30 (2m0s ago)</t>
+  </si>
+  <si>
+    <t>Leader stale?</t>
+  </si>
+  <si>
     <t>No</t>
   </si>
   <si>
-    <t>Current leader</t>
-  </si>
-  <si>
-    <t>(no leader recorded)</t>
-  </si>
-  <si>
-    <t>Leader last update</t>
-  </si>
-  <si>
-    <t>(never)</t>
-  </si>
-  <si>
-    <t>Leader stale?</t>
-  </si>
-  <si>
     <t>Last check</t>
   </si>
   <si>
     <t>Check count</t>
   </si>
   <si>
-    <t>0</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -240,9 +240,6 @@
     <t>renewed</t>
   </si>
   <si>
-    <t>github</t>
-  </si>
-  <si>
     <t>2026-06-22T07:56:01.8822385+05:30</t>
   </si>
   <si>
@@ -573,10 +570,16 @@
     <t>10:13:01.434</t>
   </si>
   <si>
+    <t>2026-07-04T10:48:12.3987015+05:30</t>
+  </si>
+  <si>
+    <t>10:48:12.398</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:45:11+05:30</t>
+    <t>2026-07-04T10:50:22+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1171,7 +1174,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 27s</t>
+          <t>0h 7m 39s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1191,7 +1194,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 24m 59s</t>
+          <t>89h 26m 19s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1201,7 +1204,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:45:11</t>
+          <t>10:50:22</t>
         </is>
       </c>
     </row>
@@ -1258,17 +1261,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>919.0</t>
+          <t>202.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>178358.6</t>
+          <t>116745.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>566</t>
+          <t>2412</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1278,7 +1281,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>340</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1298,7 +1301,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 24m 9s</t>
+          <t>89h 26m 9s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1308,7 +1311,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:45:11</t>
+          <t>10:50:22</t>
         </is>
       </c>
     </row>
@@ -1427,7 +1430,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T10:13:01.4343984+05:30</t>
+          <t>2026-07-04T10:48:12.3987015+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1437,7 +1440,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:13:01.434</t>
+          <t>10:48:12.398</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1761,23 +1764,23 @@
         <v>16</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="2" t="s">
         <v>18</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="2" t="s">
         <v>20</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="12">
@@ -1785,7 +1788,7 @@
         <v>21</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -2407,7 +2410,7 @@
         <v>73</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G32" s="4" t="s">
         <v>9</v>
@@ -2433,19 +2436,19 @@
         <v>16</v>
       </c>
       <c r="B33" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="C33" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="D33" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="D33" s="3" t="s">
+      <c r="E33" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="E33" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="F33" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G33" s="3" t="s">
         <v>9</v>
@@ -2460,10 +2463,10 @@
         <v>9223372036</v>
       </c>
       <c r="K33" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L33" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L33" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="34">
@@ -2471,19 +2474,19 @@
         <v>17</v>
       </c>
       <c r="B34" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C34" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="C34" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D34" s="3" t="s">
-        <v>81</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G34" s="3" t="s">
         <v>9</v>
@@ -2498,10 +2501,10 @@
         <v>9223372036</v>
       </c>
       <c r="K34" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L34" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L34" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="35">
@@ -2509,19 +2512,19 @@
         <v>18</v>
       </c>
       <c r="B35" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="C35" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="C35" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D35" s="3" t="s">
-        <v>83</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G35" s="3" t="s">
         <v>9</v>
@@ -2536,10 +2539,10 @@
         <v>9223372036</v>
       </c>
       <c r="K35" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L35" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L35" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="36">
@@ -2547,19 +2550,19 @@
         <v>19</v>
       </c>
       <c r="B36" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="C36" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="C36" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="3" t="s">
-        <v>85</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G36" s="3" t="s">
         <v>9</v>
@@ -2574,10 +2577,10 @@
         <v>9223372036</v>
       </c>
       <c r="K36" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L36" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L36" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="37">
@@ -2585,19 +2588,19 @@
         <v>20</v>
       </c>
       <c r="B37" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C37" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="D37" s="3" t="s">
-        <v>87</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G37" s="3" t="s">
         <v>9</v>
@@ -2612,10 +2615,10 @@
         <v>9223372036</v>
       </c>
       <c r="K37" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="L37" s="3" t="s">
         <v>78</v>
-      </c>
-      <c r="L37" s="3" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="38">
@@ -2623,19 +2626,19 @@
         <v>21</v>
       </c>
       <c r="B38" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="D38" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="C38" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>89</v>
-      </c>
       <c r="E38" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G38" s="4" t="s">
         <v>9</v>
@@ -2661,19 +2664,19 @@
         <v>22</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="E39" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="E39" s="2" t="s">
-        <v>93</v>
-      </c>
       <c r="F39" s="2" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>9</v>
@@ -2688,7 +2691,7 @@
         <v>0</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>44</v>
@@ -2699,19 +2702,19 @@
         <v>23</v>
       </c>
       <c r="B40" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="C40" s="4" t="s">
+      <c r="D40" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D40" s="4" t="s">
-        <v>96</v>
-      </c>
       <c r="E40" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G40" s="4" t="s">
         <v>9</v>
@@ -2737,19 +2740,19 @@
         <v>24</v>
       </c>
       <c r="B41" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="C41" s="4" t="s">
+      <c r="D41" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="D41" s="4" t="s">
-        <v>99</v>
-      </c>
       <c r="E41" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G41" s="4" t="s">
         <v>9</v>
@@ -2775,19 +2778,19 @@
         <v>25</v>
       </c>
       <c r="B42" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D42" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="C42" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D42" s="4" t="s">
-        <v>101</v>
-      </c>
       <c r="E42" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G42" s="4" t="s">
         <v>9</v>
@@ -2813,19 +2816,19 @@
         <v>26</v>
       </c>
       <c r="B43" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="C43" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>103</v>
-      </c>
       <c r="E43" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G43" s="4" t="s">
         <v>9</v>
@@ -2851,19 +2854,19 @@
         <v>27</v>
       </c>
       <c r="B44" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D44" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="C44" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D44" s="4" t="s">
-        <v>105</v>
-      </c>
       <c r="E44" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G44" s="4" t="s">
         <v>9</v>
@@ -2889,19 +2892,19 @@
         <v>28</v>
       </c>
       <c r="B45" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D45" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="C45" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D45" s="4" t="s">
-        <v>107</v>
-      </c>
       <c r="E45" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G45" s="4" t="s">
         <v>9</v>
@@ -2927,19 +2930,19 @@
         <v>29</v>
       </c>
       <c r="B46" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D46" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C46" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D46" s="4" t="s">
-        <v>109</v>
-      </c>
       <c r="E46" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G46" s="4" t="s">
         <v>9</v>
@@ -2965,19 +2968,19 @@
         <v>30</v>
       </c>
       <c r="B47" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D47" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="C47" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D47" s="4" t="s">
-        <v>111</v>
-      </c>
       <c r="E47" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G47" s="4" t="s">
         <v>9</v>
@@ -3003,19 +3006,19 @@
         <v>31</v>
       </c>
       <c r="B48" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D48" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="C48" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>113</v>
-      </c>
       <c r="E48" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F48" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G48" s="4" t="s">
         <v>9</v>
@@ -3041,19 +3044,19 @@
         <v>32</v>
       </c>
       <c r="B49" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D49" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="C49" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>115</v>
-      </c>
       <c r="E49" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G49" s="4" t="s">
         <v>9</v>
@@ -3079,19 +3082,19 @@
         <v>33</v>
       </c>
       <c r="B50" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D50" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="C50" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D50" s="4" t="s">
-        <v>117</v>
-      </c>
       <c r="E50" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G50" s="4" t="s">
         <v>9</v>
@@ -3117,19 +3120,19 @@
         <v>34</v>
       </c>
       <c r="B51" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D51" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="C51" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>119</v>
-      </c>
       <c r="E51" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G51" s="4" t="s">
         <v>9</v>
@@ -3155,19 +3158,19 @@
         <v>35</v>
       </c>
       <c r="B52" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D52" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C52" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>121</v>
-      </c>
       <c r="E52" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G52" s="4" t="s">
         <v>9</v>
@@ -3193,19 +3196,19 @@
         <v>36</v>
       </c>
       <c r="B53" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D53" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="C53" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D53" s="4" t="s">
-        <v>123</v>
-      </c>
       <c r="E53" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G53" s="4" t="s">
         <v>9</v>
@@ -3231,19 +3234,19 @@
         <v>37</v>
       </c>
       <c r="B54" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D54" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="C54" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>125</v>
-      </c>
       <c r="E54" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G54" s="4" t="s">
         <v>9</v>
@@ -3269,19 +3272,19 @@
         <v>38</v>
       </c>
       <c r="B55" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D55" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="C55" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D55" s="4" t="s">
-        <v>127</v>
-      </c>
       <c r="E55" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G55" s="4" t="s">
         <v>9</v>
@@ -3307,19 +3310,19 @@
         <v>39</v>
       </c>
       <c r="B56" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D56" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="C56" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D56" s="4" t="s">
-        <v>129</v>
-      </c>
       <c r="E56" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G56" s="4" t="s">
         <v>9</v>
@@ -3345,19 +3348,19 @@
         <v>40</v>
       </c>
       <c r="B57" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D57" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="C57" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>131</v>
-      </c>
       <c r="E57" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G57" s="4" t="s">
         <v>9</v>
@@ -3383,19 +3386,19 @@
         <v>41</v>
       </c>
       <c r="B58" s="4" t="s">
+        <v>131</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D58" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="C58" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D58" s="4" t="s">
-        <v>133</v>
-      </c>
       <c r="E58" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G58" s="4" t="s">
         <v>9</v>
@@ -3421,19 +3424,19 @@
         <v>42</v>
       </c>
       <c r="B59" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="C59" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>135</v>
-      </c>
       <c r="E59" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G59" s="4" t="s">
         <v>9</v>
@@ -3459,19 +3462,19 @@
         <v>43</v>
       </c>
       <c r="B60" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D60" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="C60" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>137</v>
-      </c>
       <c r="E60" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G60" s="4" t="s">
         <v>9</v>
@@ -3497,19 +3500,19 @@
         <v>44</v>
       </c>
       <c r="B61" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D61" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="C61" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D61" s="4" t="s">
-        <v>139</v>
-      </c>
       <c r="E61" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G61" s="4" t="s">
         <v>9</v>
@@ -3535,19 +3538,19 @@
         <v>45</v>
       </c>
       <c r="B62" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D62" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="C62" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D62" s="4" t="s">
-        <v>141</v>
-      </c>
       <c r="E62" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G62" s="4" t="s">
         <v>9</v>
@@ -3573,19 +3576,19 @@
         <v>46</v>
       </c>
       <c r="B63" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D63" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C63" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D63" s="4" t="s">
-        <v>143</v>
-      </c>
       <c r="E63" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G63" s="4" t="s">
         <v>9</v>
@@ -3611,19 +3614,19 @@
         <v>47</v>
       </c>
       <c r="B64" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D64" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C64" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>145</v>
-      </c>
       <c r="E64" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G64" s="4" t="s">
         <v>9</v>
@@ -3649,19 +3652,19 @@
         <v>48</v>
       </c>
       <c r="B65" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D65" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="C65" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D65" s="4" t="s">
-        <v>147</v>
-      </c>
       <c r="E65" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G65" s="4" t="s">
         <v>9</v>
@@ -3687,19 +3690,19 @@
         <v>49</v>
       </c>
       <c r="B66" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="C66" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="C66" s="4" t="s">
+      <c r="D66" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="D66" s="4" t="s">
-        <v>150</v>
-      </c>
       <c r="E66" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G66" s="4" t="s">
         <v>9</v>
@@ -3725,19 +3728,19 @@
         <v>50</v>
       </c>
       <c r="B67" s="4" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D67" s="4" t="s">
         <v>151</v>
       </c>
-      <c r="C67" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>152</v>
-      </c>
       <c r="E67" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G67" s="4" t="s">
         <v>9</v>
@@ -3763,19 +3766,19 @@
         <v>51</v>
       </c>
       <c r="B68" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D68" s="4" t="s">
         <v>153</v>
       </c>
-      <c r="C68" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D68" s="4" t="s">
-        <v>154</v>
-      </c>
       <c r="E68" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G68" s="4" t="s">
         <v>9</v>
@@ -3801,19 +3804,19 @@
         <v>52</v>
       </c>
       <c r="B69" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="D69" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="C69" s="4" t="s">
-        <v>149</v>
-      </c>
-      <c r="D69" s="4" t="s">
-        <v>156</v>
-      </c>
       <c r="E69" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G69" s="4" t="s">
         <v>9</v>
@@ -3839,19 +3842,19 @@
         <v>53</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" s="4" t="s">
         <v>157</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="D70" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="D70" s="4" t="s">
-        <v>159</v>
-      </c>
       <c r="E70" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G70" s="4" t="s">
         <v>9</v>
@@ -3877,19 +3880,19 @@
         <v>54</v>
       </c>
       <c r="B71" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D71" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="C71" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D71" s="4" t="s">
-        <v>161</v>
-      </c>
       <c r="E71" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G71" s="4" t="s">
         <v>9</v>
@@ -3915,19 +3918,19 @@
         <v>55</v>
       </c>
       <c r="B72" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D72" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C72" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D72" s="4" t="s">
-        <v>163</v>
-      </c>
       <c r="E72" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G72" s="4" t="s">
         <v>9</v>
@@ -3953,19 +3956,19 @@
         <v>56</v>
       </c>
       <c r="B73" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="D73" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>158</v>
-      </c>
-      <c r="D73" s="4" t="s">
-        <v>165</v>
-      </c>
       <c r="E73" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G73" s="4" t="s">
         <v>9</v>
@@ -3991,19 +3994,19 @@
         <v>57</v>
       </c>
       <c r="B74" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="C74" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="D74" s="4" t="s">
         <v>167</v>
       </c>
-      <c r="D74" s="4" t="s">
-        <v>168</v>
-      </c>
       <c r="E74" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G74" s="4" t="s">
         <v>9</v>
@@ -4029,19 +4032,19 @@
         <v>58</v>
       </c>
       <c r="B75" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D75" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="C75" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D75" s="4" t="s">
-        <v>170</v>
-      </c>
       <c r="E75" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G75" s="4" t="s">
         <v>9</v>
@@ -4067,19 +4070,19 @@
         <v>59</v>
       </c>
       <c r="B76" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D76" s="4" t="s">
         <v>171</v>
       </c>
-      <c r="C76" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D76" s="4" t="s">
-        <v>172</v>
-      </c>
       <c r="E76" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G76" s="4" t="s">
         <v>9</v>
@@ -4105,19 +4108,19 @@
         <v>60</v>
       </c>
       <c r="B77" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>173</v>
       </c>
-      <c r="C77" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>174</v>
-      </c>
       <c r="E77" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G77" s="4" t="s">
         <v>9</v>
@@ -4143,19 +4146,19 @@
         <v>61</v>
       </c>
       <c r="B78" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D78" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="C78" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D78" s="4" t="s">
-        <v>176</v>
-      </c>
       <c r="E78" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G78" s="4" t="s">
         <v>9</v>
@@ -4181,19 +4184,19 @@
         <v>62</v>
       </c>
       <c r="B79" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D79" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="C79" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D79" s="4" t="s">
-        <v>178</v>
-      </c>
       <c r="E79" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G79" s="4" t="s">
         <v>9</v>
@@ -4219,19 +4222,19 @@
         <v>63</v>
       </c>
       <c r="B80" s="4" t="s">
+        <v>178</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D80" s="4" t="s">
         <v>179</v>
       </c>
-      <c r="C80" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D80" s="4" t="s">
-        <v>180</v>
-      </c>
       <c r="E80" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G80" s="4" t="s">
         <v>9</v>
@@ -4257,19 +4260,19 @@
         <v>64</v>
       </c>
       <c r="B81" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D81" s="4" t="s">
         <v>181</v>
       </c>
-      <c r="C81" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D81" s="4" t="s">
-        <v>182</v>
-      </c>
       <c r="E81" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>74</v>
+        <v>3</v>
       </c>
       <c r="G81" s="4" t="s">
         <v>9</v>
@@ -4295,51 +4298,89 @@
         <v>65</v>
       </c>
       <c r="B82" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D82" s="4" t="s">
         <v>183</v>
       </c>
-      <c r="C82" s="4" t="s">
-        <v>167</v>
-      </c>
-      <c r="D82" s="4" t="s">
+      <c r="E82" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F82" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H82" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I82" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J82" s="4">
+        <v>0</v>
+      </c>
+      <c r="K82" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L82" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4">
+        <v>66</v>
+      </c>
+      <c r="B83" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="E82" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="F82" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="G82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="H82" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="I82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="J82" s="4">
-        <v>0</v>
-      </c>
-      <c r="K82" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="L82" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="s">
+      <c r="C83" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D83" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="B84" t="s">
+      <c r="E83" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F83" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H83" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I83" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J83" s="4">
+        <v>0</v>
+      </c>
+      <c r="K83" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L83" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="s">
         <v>186</v>
       </c>
-      <c r="D84" t="s">
+      <c r="B85" t="s">
         <v>187</v>
       </c>
-      <c r="E84">
-        <v>65</v>
+      <c r="D85" t="s">
+        <v>188</v>
+      </c>
+      <c r="E85">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:50:22+05:30</t>
+    <t>Generated 2026-07-04T10:55:28+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:48:22+05:30 (2m0s ago)</t>
+    <t>2026-07-04T10:53:28+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>Last error</t>
@@ -576,10 +576,16 @@
     <t>10:48:12.398</t>
   </si>
   <si>
+    <t>2026-07-04T10:53:12.4339202+05:30</t>
+  </si>
+  <si>
+    <t>10:53:12.433</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:50:22+05:30</t>
+    <t>2026-07-04T10:55:28+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1174,7 +1180,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 39s</t>
+          <t>0h 12m 45s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1194,7 +1200,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 26m 19s</t>
+          <t>89h 27m 29s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1204,7 +1210,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:50:22</t>
+          <t>10:55:28</t>
         </is>
       </c>
     </row>
@@ -1261,17 +1267,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>202.0</t>
+          <t>567.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>116745.6</t>
+          <t>163440.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2412</t>
+          <t>3405</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1281,7 +1287,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>340</t>
+          <t>645</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1301,7 +1307,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 26m 9s</t>
+          <t>89h 27m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1311,7 +1317,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:50:22</t>
+          <t>10:55:28</t>
         </is>
       </c>
     </row>
@@ -1430,7 +1436,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T10:48:12.3987015+05:30</t>
+          <t>2026-07-04T10:53:12.4339202+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1440,7 +1446,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:48:12.398</t>
+          <t>10:53:12.433</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4369,18 +4375,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" t="s">
+    <row r="84">
+      <c r="A84" s="4">
+        <v>67</v>
+      </c>
+      <c r="B84" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C84" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D84" s="4" t="s">
         <v>187</v>
       </c>
-      <c r="D85" t="s">
+      <c r="E84" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F84" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H84" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I84" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J84" s="4">
+        <v>0</v>
+      </c>
+      <c r="K84" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L84" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="s">
         <v>188</v>
       </c>
-      <c r="E85">
-        <v>66</v>
+      <c r="B86" t="s">
+        <v>189</v>
+      </c>
+      <c r="D86" t="s">
+        <v>190</v>
+      </c>
+      <c r="E86">
+        <v>67</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="193">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T10:55:28+05:30</t>
+    <t>Generated 2026-07-04T11:00:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T10:53:28+05:30 (2m0s ago)</t>
+    <t>2026-07-04T10:58:13+05:30 (2m3s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -582,10 +582,16 @@
     <t>10:53:12.433</t>
   </si>
   <si>
+    <t>2026-07-04T10:58:13.8602988+05:30</t>
+  </si>
+  <si>
+    <t>10:58:13.860</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T10:55:28+05:30</t>
+    <t>2026-07-04T11:00:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1140,7 +1146,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.62</t>
+          <t>10.0.63</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1180,12 +1186,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 45s</t>
+          <t>0h 2m 19s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-04 10:42:43</t>
+          <t>2026-07-04 10:57:57</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1195,12 +1201,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-07-04 10:42:43</t>
+          <t>2026-07-04 10:57:57</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 27m 29s</t>
+          <t>89h 28m 24s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1210,7 +1216,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>10:55:28</t>
+          <t>11:00:17</t>
         </is>
       </c>
     </row>
@@ -1247,7 +1253,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.62</t>
+          <t>10.0.63</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1267,17 +1273,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>567.0</t>
+          <t>115.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>163440.4</t>
+          <t>85889.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>822</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1287,7 +1293,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>645</t>
+          <t>19</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1302,12 +1308,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-07-04 10:42:43</t>
+          <t>2026-07-04 10:57:57</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 27m 19s</t>
+          <t>89h 27m 29s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1317,7 +1323,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>10:55:28</t>
+          <t>11:00:17</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1442,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T10:53:12.4339202+05:30</t>
+          <t>2026-07-04T10:58:13.8602988+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1446,7 +1452,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10:53:12.433</t>
+          <t>10:58:13.860</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4413,18 +4419,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" t="s">
+    <row r="85">
+      <c r="A85" s="4">
+        <v>68</v>
+      </c>
+      <c r="B85" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B86" t="s">
+      <c r="C85" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D85" s="4" t="s">
         <v>189</v>
       </c>
-      <c r="D86" t="s">
+      <c r="E85" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F85" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H85" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I85" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J85" s="4">
+        <v>0</v>
+      </c>
+      <c r="K85" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L85" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="s">
         <v>190</v>
       </c>
-      <c r="E86">
-        <v>67</v>
+      <c r="B87" t="s">
+        <v>191</v>
+      </c>
+      <c r="D87" t="s">
+        <v>192</v>
+      </c>
+      <c r="E87">
+        <v>68</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T11:08:57+05:30</t>
+    <t>Generated 2026-07-04T11:14:14+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T11:06:52+05:30 (2m5s ago)</t>
+    <t>2026-07-04T11:12:14+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>1</t>
+    <t>3</t>
   </si>
   <si>
     <t>Last error</t>
@@ -594,10 +594,16 @@
     <t>11:06:52.447</t>
   </si>
   <si>
+    <t>2026-07-04T11:11:58.9279547+05:30</t>
+  </si>
+  <si>
+    <t>11:11:58.927</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T11:08:57+05:30</t>
+    <t>2026-07-04T11:14:14+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1192,7 +1198,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 2m 19s</t>
+          <t>0h 7m 36s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1212,7 +1218,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 28m 54s</t>
+          <t>89h 29m 54s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1222,7 +1228,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>11:08:57</t>
+          <t>11:14:14</t>
         </is>
       </c>
     </row>
@@ -1279,17 +1285,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>225.0</t>
+          <t>315.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>193664.6</t>
+          <t>110384.6</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>587</t>
+          <t>1934</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1299,7 +1305,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>337</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1319,7 +1325,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 28m 49s</t>
+          <t>89h 28m 54s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1329,7 +1335,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>11:08:57</t>
+          <t>11:14:14</t>
         </is>
       </c>
     </row>
@@ -1448,7 +1454,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T11:06:52.4478668+05:30</t>
+          <t>2026-07-04T11:11:58.9279547+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1458,7 +1464,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:06:52.447</t>
+          <t>11:11:58.927</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4501,18 +4507,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" t="s">
+    <row r="87">
+      <c r="A87" s="4">
+        <v>70</v>
+      </c>
+      <c r="B87" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B88" t="s">
+      <c r="C87" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D87" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="D88" t="s">
+      <c r="E87" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F87" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H87" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I87" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J87" s="4">
+        <v>0</v>
+      </c>
+      <c r="K87" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L87" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="s">
         <v>194</v>
       </c>
-      <c r="E88">
-        <v>69</v>
+      <c r="B89" t="s">
+        <v>195</v>
+      </c>
+      <c r="D89" t="s">
+        <v>196</v>
+      </c>
+      <c r="E89">
+        <v>70</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T11:14:14+05:30</t>
+    <t>Generated 2026-07-04T11:19:17+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T11:12:14+05:30 (2m0s ago)</t>
+    <t>2026-07-04T11:17:17+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>3</t>
+    <t>5</t>
   </si>
   <si>
     <t>Last error</t>
@@ -600,10 +600,16 @@
     <t>11:11:58.927</t>
   </si>
   <si>
+    <t>2026-07-04T11:16:58.9384123+05:30</t>
+  </si>
+  <si>
+    <t>11:16:58.938</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T11:14:14+05:30</t>
+    <t>2026-07-04T11:19:17+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1198,7 +1204,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 7m 36s</t>
+          <t>0h 12m 39s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1218,7 +1224,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 29m 54s</t>
+          <t>89h 30m 24s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1228,7 +1234,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>11:14:14</t>
+          <t>11:19:17</t>
         </is>
       </c>
     </row>
@@ -1285,17 +1291,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>315.0</t>
+          <t>122.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>110384.6</t>
+          <t>138182.4</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>1934</t>
+          <t>3441</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1305,7 +1311,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>337</t>
+          <t>639</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1325,7 +1331,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 28m 54s</t>
+          <t>89h 30m 19s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1335,7 +1341,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>11:14:14</t>
+          <t>11:19:17</t>
         </is>
       </c>
     </row>
@@ -1454,7 +1460,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T11:11:58.9279547+05:30</t>
+          <t>2026-07-04T11:16:58.9384123+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1464,7 +1470,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:11:58.927</t>
+          <t>11:16:58.938</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4545,18 +4551,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="s">
+    <row r="88">
+      <c r="A88" s="4">
+        <v>71</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B89" t="s">
+      <c r="C88" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D88" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D89" t="s">
+      <c r="E88" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F88" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H88" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I88" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J88" s="4">
+        <v>0</v>
+      </c>
+      <c r="K88" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L88" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="s">
         <v>196</v>
       </c>
-      <c r="E89">
-        <v>70</v>
+      <c r="B90" t="s">
+        <v>197</v>
+      </c>
+      <c r="D90" t="s">
+        <v>198</v>
+      </c>
+      <c r="E90">
+        <v>71</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T11:19:17+05:30</t>
+    <t>Generated 2026-07-04T11:24:11+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T11:17:17+05:30 (2m0s ago)</t>
+    <t>2026-07-04T11:22:31+05:30 (1m39s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>5</t>
+    <t>7</t>
   </si>
   <si>
     <t>Last error</t>
@@ -606,10 +606,16 @@
     <t>11:16:58.938</t>
   </si>
   <si>
+    <t>2026-07-04T11:22:11.162157+05:30</t>
+  </si>
+  <si>
+    <t>11:22:11.162</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T11:19:17+05:30</t>
+    <t>2026-07-04T11:24:11+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1204,7 +1210,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 12m 39s</t>
+          <t>0h 17m 33s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1224,7 +1230,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 30m 24s</t>
+          <t>89h 31m 9s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1234,7 +1240,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>11:19:17</t>
+          <t>11:24:11</t>
         </is>
       </c>
     </row>
@@ -1291,17 +1297,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>122.0</t>
+          <t>201.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>138182.4</t>
+          <t>238856.2</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1311,7 +1317,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>954</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1331,7 +1337,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 30m 19s</t>
+          <t>89h 31m 9s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1341,7 +1347,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>11:19:17</t>
+          <t>11:24:11</t>
         </is>
       </c>
     </row>
@@ -1460,7 +1466,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T11:16:58.9384123+05:30</t>
+          <t>2026-07-04T11:22:11.162157+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1470,7 +1476,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:16:58.938</t>
+          <t>11:22:11.162</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4589,18 +4595,56 @@
         <v>44</v>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="s">
+    <row r="89">
+      <c r="A89" s="4">
+        <v>72</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B90" t="s">
+      <c r="C89" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D89" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="D90" t="s">
+      <c r="E89" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F89" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H89" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I89" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J89" s="4">
+        <v>0</v>
+      </c>
+      <c r="K89" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L89" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="s">
         <v>198</v>
       </c>
-      <c r="E90">
-        <v>71</v>
+      <c r="B91" t="s">
+        <v>199</v>
+      </c>
+      <c r="D91" t="s">
+        <v>200</v>
+      </c>
+      <c r="E91">
+        <v>72</v>
       </c>
     </row>
   </sheetData>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -21,7 +21,7 @@
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T11:24:11+05:30</t>
+    <t>Generated 2026-07-04T11:24:31+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T11:22:31+05:30 (1m39s ago)</t>
+    <t>2026-07-04T11:22:31+05:30 (2m0s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -615,7 +615,7 @@
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T11:24:11+05:30</t>
+    <t>2026-07-04T11:24:31+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 33s</t>
+          <t>0h 17m 54s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -1240,7 +1240,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>11:24:11</t>
+          <t>11:24:31</t>
         </is>
       </c>
     </row>
@@ -1297,17 +1297,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>201.0</t>
+          <t>136.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>238856.2</t>
+          <t>150611.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5110</t>
+          <t>5190</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1347,7 +1347,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>11:24:11</t>
+          <t>11:24:31</t>
         </is>
       </c>
     </row>

--- a/report-2026-07-04.xlsx
+++ b/report-2026-07-04.xlsx
@@ -16,12 +16,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="209">
   <si>
     <t>PunMonitor Leader Election — Current State</t>
   </si>
   <si>
-    <t>Generated 2026-07-04T11:24:31+05:30</t>
+    <t>Generated 2026-07-04T11:34:09+05:30</t>
   </si>
   <si>
     <t>Election method</t>
@@ -72,7 +72,7 @@
     <t>Leader last update</t>
   </si>
   <si>
-    <t>2026-07-04T11:22:31+05:30 (2m0s ago)</t>
+    <t>2026-07-04T11:32:05+05:30 (2m4s ago)</t>
   </si>
   <si>
     <t>Leader stale?</t>
@@ -87,7 +87,7 @@
     <t>Check count</t>
   </si>
   <si>
-    <t>7</t>
+    <t>1</t>
   </si>
   <si>
     <t>Last error</t>
@@ -612,10 +612,34 @@
     <t>11:22:11.162</t>
   </si>
   <si>
+    <t>2026-07-04T11:27:09.2659556+05:30</t>
+  </si>
+  <si>
+    <t>11:27:09.265</t>
+  </si>
+  <si>
+    <t>2026-07-04T11:28:39.5757129+05:30</t>
+  </si>
+  <si>
+    <t>11:28:39.575</t>
+  </si>
+  <si>
+    <t>2026-07-04T11:30:00.5720281+05:30</t>
+  </si>
+  <si>
+    <t>11:30:00.572</t>
+  </si>
+  <si>
+    <t>2026-07-04T11:32:05.0654897+05:30</t>
+  </si>
+  <si>
+    <t>11:32:05.065</t>
+  </si>
+  <si>
     <t>Generated</t>
   </si>
   <si>
-    <t>2026-07-04T11:24:31+05:30</t>
+    <t>2026-07-04T11:34:09+05:30</t>
   </si>
   <si>
     <t>Total events</t>
@@ -1170,7 +1194,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>10.0.63</t>
+          <t>10.0.64</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -1210,12 +1234,12 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0h 17m 54s</t>
+          <t>0h 2m 19s</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-07-04 11:06:37</t>
+          <t>2026-07-04 11:31:49</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
@@ -1225,12 +1249,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>2026-07-04 11:06:37</t>
+          <t>2026-07-04 11:31:49</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>89h 31m 9s</t>
+          <t>89h 32m 14s</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -1240,7 +1264,7 @@
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>11:24:31</t>
+          <t>11:34:09</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1301,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>10.0.63</t>
+          <t>10.0.64</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -1297,17 +1321,17 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>136.0</t>
+          <t>190.0</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>150611.0</t>
+          <t>149371.0</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>5190</t>
+          <t>569</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -1317,7 +1341,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -1332,12 +1356,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>2026-07-04 11:06:37</t>
+          <t>2026-07-04 11:31:49</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>89h 31m 9s</t>
+          <t>89h 32m 9s</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1347,7 +1371,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>11:24:31</t>
+          <t>11:34:09</t>
         </is>
       </c>
     </row>
@@ -1466,7 +1490,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-07-04T11:22:11.162157+05:30</t>
+          <t>2026-07-04T11:32:05.0654897+05:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1476,7 +1500,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11:22:11.162</t>
+          <t>11:32:05.065</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -4633,18 +4657,170 @@
         <v>44</v>
       </c>
     </row>
+    <row r="90">
+      <c r="A90" s="4">
+        <v>73</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D90" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="E90" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F90" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H90" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I90" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J90" s="4">
+        <v>0</v>
+      </c>
+      <c r="K90" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L90" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
     <row r="91">
-      <c r="A91" t="s">
-        <v>198</v>
-      </c>
-      <c r="B91" t="s">
-        <v>199</v>
-      </c>
-      <c r="D91" t="s">
+      <c r="A91" s="4">
+        <v>74</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="E91">
-        <v>72</v>
+      <c r="C91" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D91" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="E91" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F91" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G91" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H91" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I91" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J91" s="4">
+        <v>0</v>
+      </c>
+      <c r="K91" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L91" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4">
+        <v>75</v>
+      </c>
+      <c r="B92" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D92" s="4" t="s">
+        <v>203</v>
+      </c>
+      <c r="E92" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F92" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G92" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H92" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I92" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J92" s="4">
+        <v>0</v>
+      </c>
+      <c r="K92" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L92" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4">
+        <v>76</v>
+      </c>
+      <c r="B93" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D93" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="E93" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="F93" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="G93" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="H93" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="I93" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="J93" s="4">
+        <v>0</v>
+      </c>
+      <c r="K93" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="L93" s="4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="s">
+        <v>206</v>
+      </c>
+      <c r="B95" t="s">
+        <v>207</v>
+      </c>
+      <c r="D95" t="s">
+        <v>208</v>
+      </c>
+      <c r="E95">
+        <v>76</v>
       </c>
     </row>
   </sheetData>
